--- a/notebooks/emerging_ai_projects/growth_rate.xlsx
+++ b/notebooks/emerging_ai_projects/growth_rate.xlsx
@@ -13155,7 +13155,7 @@
         <v>352</v>
       </c>
       <c r="H12">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -13164,13 +13164,13 @@
         <v>122</v>
       </c>
       <c r="K12">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="L12" t="s">
         <v>63</v>
       </c>
       <c r="M12">
-        <v>-111.4335883047567</v>
+        <v>-109.7053441898819</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -13196,7 +13196,7 @@
         <v>265</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -13205,13 +13205,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="L13" t="s">
         <v>63</v>
       </c>
       <c r="M13">
-        <v>-63.91633725607689</v>
+        <v>-55.37916596494341</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -13647,7 +13647,7 @@
         <v>6796</v>
       </c>
       <c r="H24">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -13656,13 +13656,13 @@
         <v>17</v>
       </c>
       <c r="K24">
-        <v>8677</v>
+        <v>8713</v>
       </c>
       <c r="L24" t="s">
         <v>63</v>
       </c>
       <c r="M24">
-        <v>-7.726405268916103</v>
+        <v>-7.312373625136459</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -13688,7 +13688,7 @@
         <v>5380</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -13697,13 +13697,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>6655</v>
+        <v>6731</v>
       </c>
       <c r="L25" t="s">
         <v>63</v>
       </c>
       <c r="M25">
-        <v>-26.53073949642781</v>
+        <v>-25.80924422205726</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -13937,19 +13937,19 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K31">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s">
         <v>63</v>
       </c>
       <c r="M31">
-        <v>-90.85085914321</v>
+        <v>-76.43746898483128</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -14303,7 +14303,7 @@
         <v>8641</v>
       </c>
       <c r="H40">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -14312,13 +14312,13 @@
         <v>10533</v>
       </c>
       <c r="K40">
-        <v>21679</v>
+        <v>21680</v>
       </c>
       <c r="L40" t="s">
         <v>63</v>
       </c>
       <c r="M40">
-        <v>-36.5707325624042</v>
+        <v>-36.56611990989767</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -14344,7 +14344,7 @@
         <v>6962</v>
       </c>
       <c r="H41">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -14353,13 +14353,13 @@
         <v>4907</v>
       </c>
       <c r="K41">
-        <v>14411</v>
+        <v>14415</v>
       </c>
       <c r="L41" t="s">
         <v>63</v>
       </c>
       <c r="M41">
-        <v>-40.83522461901552</v>
+        <v>-40.81208454810792</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -14385,7 +14385,7 @@
         <v>4499</v>
       </c>
       <c r="H42">
-        <v>134</v>
+        <v>850</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -14394,13 +14394,13 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>5922</v>
+        <v>6638</v>
       </c>
       <c r="L42" t="s">
         <v>63</v>
       </c>
       <c r="M42">
-        <v>-88.93175741768253</v>
+        <v>-77.54586177925837</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -14426,7 +14426,7 @@
         <v>3216</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -14435,13 +14435,13 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>4146</v>
+        <v>4485</v>
       </c>
       <c r="L43" t="s">
         <v>63</v>
       </c>
       <c r="M43">
-        <v>-35.65302156658117</v>
+        <v>-39.20722177870228</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -14631,7 +14631,7 @@
         <v>911</v>
       </c>
       <c r="H48">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -14640,13 +14640,13 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="L48" t="s">
         <v>63</v>
       </c>
       <c r="M48">
-        <v>-78.58689206101684</v>
+        <v>-76.94173157181625</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -14672,7 +14672,7 @@
         <v>1200</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -14681,13 +14681,13 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>1295</v>
+        <v>1400</v>
       </c>
       <c r="L49" t="s">
         <v>63</v>
       </c>
       <c r="M49">
-        <v>2.26483714295167</v>
+        <v>8.415830800722279</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -14877,7 +14877,7 @@
         <v>352</v>
       </c>
       <c r="H54">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -14886,13 +14886,13 @@
         <v>24</v>
       </c>
       <c r="K54">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="L54" t="s">
         <v>63</v>
       </c>
       <c r="M54">
-        <v>-113.0550050517194</v>
+        <v>-109.9678386850107</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -14918,7 +14918,7 @@
         <v>145</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -14927,13 +14927,13 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="L55" t="s">
         <v>63</v>
       </c>
       <c r="M55">
-        <v>-94.72944719251552</v>
+        <v>-78.52624694677503</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -16151,19 +16151,19 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L85" t="s">
         <v>64</v>
       </c>
       <c r="M85">
-        <v>-28.76820724517808</v>
+        <v>-13.35313926245227</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -16845,7 +16845,7 @@
         <v>1514</v>
       </c>
       <c r="H102">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -16854,13 +16854,13 @@
         <v>183</v>
       </c>
       <c r="K102">
-        <v>2238</v>
+        <v>2301</v>
       </c>
       <c r="L102" t="s">
         <v>62</v>
       </c>
       <c r="M102">
-        <v>-61.87298184176777</v>
+        <v>-59.09686172541821</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -16886,7 +16886,7 @@
         <v>1354</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -16895,13 +16895,13 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>1605</v>
+        <v>1725</v>
       </c>
       <c r="L103" t="s">
         <v>62</v>
       </c>
       <c r="M103">
-        <v>-33.24588533077542</v>
+        <v>-28.81167605699062</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -17583,7 +17583,7 @@
         <v>87</v>
       </c>
       <c r="H120">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -17592,13 +17592,13 @@
         <v>56</v>
       </c>
       <c r="K120">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L120" t="s">
         <v>64</v>
       </c>
       <c r="M120">
-        <v>142.3108334242607</v>
+        <v>142.9114358302819</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -17624,7 +17624,7 @@
         <v>28</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -17633,13 +17633,13 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L121" t="s">
         <v>64</v>
       </c>
       <c r="M121">
-        <v>-155.663972686713</v>
+        <v>-131.1331322646436</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -19598,16 +19598,16 @@
         <v>3</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K169">
-        <v>732</v>
+        <v>785</v>
       </c>
       <c r="L169" t="s">
         <v>65</v>
       </c>
       <c r="M169">
-        <v>225.1975092107627</v>
+        <v>232.1878295928724</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -22011,7 +22011,7 @@
         <v>1288</v>
       </c>
       <c r="H228">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -22020,13 +22020,13 @@
         <v>119</v>
       </c>
       <c r="K228">
-        <v>2023</v>
+        <v>2082</v>
       </c>
       <c r="L228" t="s">
         <v>66</v>
       </c>
       <c r="M228">
-        <v>-93.92577809658249</v>
+        <v>-91.05103689586569</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -22052,7 +22052,7 @@
         <v>808</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -22061,13 +22061,13 @@
         <v>0</v>
       </c>
       <c r="K229">
-        <v>1009</v>
+        <v>1132</v>
       </c>
       <c r="L229" t="s">
         <v>66</v>
       </c>
       <c r="M229">
-        <v>-69.56218168141373</v>
+        <v>-60.93429904117853</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -22503,7 +22503,7 @@
         <v>1424</v>
       </c>
       <c r="H240">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="I240">
         <v>0</v>
@@ -22512,13 +22512,13 @@
         <v>981</v>
       </c>
       <c r="K240">
-        <v>2856</v>
+        <v>2904</v>
       </c>
       <c r="L240" t="s">
         <v>66</v>
       </c>
       <c r="M240">
-        <v>-60.0773860428931</v>
+        <v>-58.41068079437193</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -22544,7 +22544,7 @@
         <v>668</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="I241">
         <v>0</v>
@@ -22553,13 +22553,13 @@
         <v>1</v>
       </c>
       <c r="K241">
-        <v>793</v>
+        <v>919</v>
       </c>
       <c r="L241" t="s">
         <v>66</v>
       </c>
       <c r="M241">
-        <v>-128.1354101824627</v>
+        <v>-115.0558253589</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I253">
         <v>0</v>
@@ -23045,13 +23045,13 @@
         <v>0</v>
       </c>
       <c r="K253">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="L253" t="s">
         <v>66</v>
       </c>
       <c r="M253">
-        <v>-244.6685436967802</v>
+        <v>-185.8898772065683</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -23487,7 +23487,7 @@
         <v>3048</v>
       </c>
       <c r="H264">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -23496,13 +23496,13 @@
         <v>490</v>
       </c>
       <c r="K264">
-        <v>4407</v>
+        <v>4427</v>
       </c>
       <c r="L264" t="s">
         <v>66</v>
       </c>
       <c r="M264">
-        <v>-12.08290938727519</v>
+        <v>-11.63011259825968</v>
       </c>
     </row>
     <row r="265" spans="1:13">
@@ -23528,7 +23528,7 @@
         <v>558</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I265">
         <v>0</v>
@@ -23537,13 +23537,13 @@
         <v>0</v>
       </c>
       <c r="K265">
-        <v>778</v>
+        <v>866</v>
       </c>
       <c r="L265" t="s">
         <v>66</v>
       </c>
       <c r="M265">
-        <v>-173.4222940663595</v>
+        <v>-163.1592524169706</v>
       </c>
     </row>
     <row r="266" spans="1:13">
@@ -24717,7 +24717,7 @@
         <v>2246</v>
       </c>
       <c r="H294">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="I294">
         <v>0</v>
@@ -24726,13 +24726,13 @@
         <v>542</v>
       </c>
       <c r="K294">
-        <v>3297</v>
+        <v>3327</v>
       </c>
       <c r="L294" t="s">
         <v>63</v>
       </c>
       <c r="M294">
-        <v>-29.94415928586882</v>
+        <v>-29.03835599119411</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -24758,7 +24758,7 @@
         <v>800</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I295">
         <v>0</v>
@@ -24767,13 +24767,13 @@
         <v>0</v>
       </c>
       <c r="K295">
-        <v>941</v>
+        <v>1069</v>
       </c>
       <c r="L295" t="s">
         <v>63</v>
       </c>
       <c r="M295">
-        <v>-125.3825103486351</v>
+        <v>-113.5347364993432</v>
       </c>
     </row>
   </sheetData>
